--- a/cartographie/PSEUDOS_A_ARBITRER.xlsx
+++ b/cartographie/PSEUDOS_A_ARBITRER.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pseudos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'pseudos'!$A$1:$F$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'pseudos'!$A$1:$G$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,15 +439,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -463,22 +464,27 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Pages</t>
+          <t>Ce que j'ai établi</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Où c'est publié</t>
+          <t>Preuve (cliquer)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Qui est-ce ?</t>
+          <t>Recettes créditées</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Commentaire</t>
+          <t>À poursuivre ?</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Ton commentaire</t>
         </is>
       </c>
     </row>
@@ -493,21 +499,28 @@
           <t>INAPORC</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>41</v>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Createur cuisine. 32 recettes creditees a son nom sur le site du lobby.</t>
+        </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>@chateau.leg0</t>
+          <t>@olivier.moulin</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -515,21 +528,28 @@
           <t>INAPORC</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>33</v>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Createur cuisine. 19 recettes creditees.</t>
+        </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>@olivier.moulin</t>
+          <t>@juliamaufay</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -537,21 +557,28 @@
           <t>INAPORC</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>31</v>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Createur cuisine. 13 recettes creditees.</t>
+        </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>@juliamaufay</t>
+          <t>@mummyfast</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -559,21 +586,28 @@
           <t>INAPORC</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>24</v>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Createur cuisine. 12 recettes creditees.</t>
+        </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>@mummyfast</t>
+          <t>@menthe_banane</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -581,21 +615,28 @@
           <t>INAPORC</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>17</v>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Jeremy, dieteticien. Notice biographique publiee par INAPORC. 5 recettes.</t>
+        </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>@julienduboue</t>
+          <t>@sophiecuisine</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -603,21 +644,28 @@
           <t>INAPORC</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
-        <v>12</v>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Sophie, creatrice cuisine. Notice biographique publiee par INAPORC. 4 recettes.</t>
+        </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>@menthe_banane</t>
+          <t>@julienduboue</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -625,21 +673,28 @@
           <t>INAPORC</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>8</v>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Julien Duboue, chef et restaurateur. 3 recettes creditees.</t>
+        </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>@sophiecuisine</t>
+          <t>@woodmoodfood</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -647,21 +702,28 @@
           <t>INAPORC</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>8</v>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Marina, creatrice cuisine. Notice biographique publiee par INAPORC. 3 recettes.</t>
+        </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>@woodmoodfood</t>
+          <t>@florianonair</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -669,21 +731,28 @@
           <t>INAPORC</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>2</v>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Florian, chaine YouTube cuisine depuis 2016. Notice publiee par INAPORC.</t>
+        </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>@florianonair</t>
+          <t>@chateau.leg0</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -691,242 +760,435 @@
           <t>INAPORC</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>2</v>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Createur cuisine. Recette creditee (creme de carottes au quinoa).</t>
+        </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1+</t>
+        </is>
+      </c>
       <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>@minireyve</t>
+          <t>@agatheduchesne_</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CNIEL</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>1</v>
+          <t>INAPORC</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Agathe Duchesne, stylisme culinaire. Notice biographique publiee par INAPORC.</t>
+        </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1+</t>
+        </is>
+      </c>
       <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>@lesprolaitiers</t>
+          <t>Mercotte (pas de pseudo)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CNIEL</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>1</v>
+          <t>INAPORC</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Jury du Meilleur Patissier (M6). Notice biographique publiee par INAPORC.</t>
+        </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>@agriskippy</t>
+          <t>Dorian (pas de pseudo)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CNIEL</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>1</v>
+          <t>INAPORC</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Blogueur cuisine depuis 2005. Notice biographique publiee par INAPORC.</t>
+        </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>@onestpret</t>
+          <t>Audrey (pas de pseudo)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CNIEL</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>1</v>
+          <t>INAPORC</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Auteure d'Audrey Cuisine, 4000 recettes. Notice publiee par INAPORC.</t>
+        </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>@valentinwerther</t>
+          <t>@gastronogeek</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CNIEL</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>1</v>
+          <t>INAPORC</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>GENERALISTE. Live Twitch avec une eleveuse, produit avec Webedia, best-of sur sa chaine YouTube. Decrit par INAPORC.</t>
+        </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>@lamourboeuf</t>
+          <t>@lebouseuh</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>1</v>
+          <t>INAPORC</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>GENERALISTE GAMING. Live Minecraft sur l'elevage porcin, best-of sur sa chaine YouTube. Decrit par INAPORC.</t>
+        </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>@interbev_fr</t>
+          <t>@agriskippy</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>1</v>
+          <t>CNIEL</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Antoine Thibault, ELEVEUR. Cite dans un article editorial, pas un partenariat.</t>
+        </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>@laviandetv</t>
+          <t>@valentinwerther</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>INTERBEV</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>1</v>
+          <t>CNIEL</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Lyceen et futur ELEVEUR. Cite dans le meme article.</t>
+        </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>@gastronogeek</t>
+          <t>@onestpret</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>INAPORC</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>1</v>
+          <t>CNIEL</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Pas une personne : hashtag de la campagne climat #OnEstPrets. Faux positif.</t>
+        </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>@lebouseuh</t>
+          <t>@minireyve</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>INAPORC</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>1</v>
+          <t>CNIEL</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>NON VERIFIE. Une seule mention, contexte non lu.</t>
+        </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
           <t>ouvrir</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>@lesprolaitiers</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>CNIEL</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>NON VERIFIE. Une seule mention, contexte non lu.</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>@lamourboeuf</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>INTERBEV</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>NON VERIFIE. Une seule mention, contexte non lu.</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>@interbev_fr</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>INTERBEV</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Compte d'INTERBEV lui-meme. A ecarter.</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>@laviandetv</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>INTERBEV</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Compte d'INTERBEV lui-meme. A ecarter.</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F21"/>
+  <autoFilter ref="A1:G25"/>
   <dataValidations count="1">
-    <dataValidation sqref="E2 E3 E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"createur remunere,createur non remunere,eleveur ou agriculteur,marque ou media du lobby,je ne sais pas"</formula1>
+    <dataValidation sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"priorite haute,priorite basse,ecarter,a verifier"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -950,6 +1212,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
